--- a/verification/cases/roundtrip/pivot_named_range/init.xlsx
+++ b/verification/cases/roundtrip/pivot_named_range/init.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="24030"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" hidePivotFieldList="1" autoCompressPictures="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A28D07C-F24C-4E2E-8C3B-F38F624CC95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8260" yWindow="1280" windowWidth="27920" windowHeight="19020" tabRatio="500"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PTWithLabelFilter" sheetId="5" r:id="rId1"/>
@@ -16,11 +22,22 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">PTRange!$A:$A,PTRange!$1:$5</definedName>
     <definedName name="PTData">Table1[#All]</definedName>
   </definedNames>
-  <calcPr calcId="140000" concurrentCalc="0"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <pivotCaches>
-    <pivotCache cacheId="51" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
     </ext>
@@ -85,7 +102,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -250,13 +267,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -269,20 +285,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" pivotButton="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
@@ -303,11 +315,19 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshOnLoad="1" refreshedBy="God" refreshedDate="41725.875190856481" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="20">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshOnLoad="1" refreshedBy="God" refreshedDate="41725.875190856481" createdVersion="4" refreshedVersion="4" minRefreshableVersion="3" recordCount="20" xr:uid="{00000000-000A-0000-FFFF-FFFF33000000}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table1"/>
   </cacheSource>
@@ -557,7 +577,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable9" cacheId="51" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A3:J15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisPage" multipleItemSelectionAllowed="1" showAll="0">
@@ -736,12 +756,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable7" cacheId="51" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0200-000001000000}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1" multipleFieldFilters="0">
   <location ref="A4:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0"/>
@@ -824,12 +847,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable8" cacheId="51" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" fieldPrintTitles="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0300-000002000000}" name="PivotTable8" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="4" minRefreshableVersion="3" useAutoFormatting="1" fieldPrintTitles="1" itemPrintTitles="1" createdVersion="4" indent="0" outline="1" outlineData="1" gridDropZones="1">
   <location ref="A4:D9" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisPage" showAll="0">
@@ -947,25 +973,28 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E21" totalsRowShown="0">
-  <autoFilter ref="A1:E21"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:E21" totalsRowShown="0">
+  <autoFilter ref="A1:E21" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="Foo"/>
-    <tableColumn id="2" name="Bar">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Foo"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Bar">
       <calculatedColumnFormula>A2*2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="Baz">
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Baz">
       <calculatedColumnFormula>IF(MOD(A2,3)=0,"fizz","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" name="Qux">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Qux">
       <calculatedColumnFormula>IF(MOD(A2,5)=0,"buzz","")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" name="Quux">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Quux">
       <calculatedColumnFormula>IF(LEN(C2&amp;D2)=0,A2,C2&amp;D2)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1294,20 +1323,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="9" width="3.1640625" customWidth="1"/>
-    <col min="10" max="10" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="17" width="3.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="21" width="3.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="3.19921875" customWidth="1"/>
+    <col min="10" max="10" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="17" width="3.19921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="3.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1315,7 +1344,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1323,7 +1352,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -1355,227 +1384,163 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
-        <v>1</v>
-      </c>
-      <c r="I5" s="3">
-        <v>1</v>
-      </c>
-      <c r="J5" s="3">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <v>7</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="4">
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>11</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3">
-        <v>1</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="4">
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <v>13</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="4">
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <v>17</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="4">
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <v>19</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="4" t="s">
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="3">
-        <v>1</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3">
-        <v>1</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3">
-        <v>1</v>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="J12">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="4" t="s">
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3">
-        <v>1</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="3">
-        <v>1</v>
-      </c>
-      <c r="C15" s="3">
-        <v>1</v>
-      </c>
-      <c r="D15" s="3">
-        <v>1</v>
-      </c>
-      <c r="E15" s="3">
-        <v>1</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1</v>
-      </c>
-      <c r="H15" s="3">
-        <v>1</v>
-      </c>
-      <c r="I15" s="3">
-        <v>1</v>
-      </c>
-      <c r="J15" s="3">
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
         <v>8</v>
       </c>
     </row>
@@ -1590,12 +1555,12 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet1" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:E21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" outlineLevelRow="3" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" outlineLevelRow="3" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1612,7 +1577,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" outlineLevel="3">
+    <row r="2" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1633,7 +1598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" outlineLevel="3">
+    <row r="3" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1654,7 +1619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" outlineLevel="3">
+    <row r="4" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1675,7 +1640,7 @@
         <v>fizz</v>
       </c>
     </row>
-    <row r="5" spans="1:5" outlineLevel="3">
+    <row r="5" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1696,7 +1661,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:5" outlineLevel="3">
+    <row r="6" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1717,7 +1682,7 @@
         <v>buzz</v>
       </c>
     </row>
-    <row r="7" spans="1:5" outlineLevel="3">
+    <row r="7" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1738,7 +1703,7 @@
         <v>fizz</v>
       </c>
     </row>
-    <row r="8" spans="1:5" outlineLevel="3">
+    <row r="8" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1759,7 +1724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:5" outlineLevel="3">
+    <row r="9" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1780,7 +1745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:5" outlineLevel="3">
+    <row r="10" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1801,7 +1766,7 @@
         <v>fizz</v>
       </c>
     </row>
-    <row r="11" spans="1:5" outlineLevel="3">
+    <row r="11" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1822,7 +1787,7 @@
         <v>buzz</v>
       </c>
     </row>
-    <row r="12" spans="1:5" outlineLevel="3">
+    <row r="12" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1843,7 +1808,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:5" outlineLevel="3">
+    <row r="13" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1864,7 +1829,7 @@
         <v>fizz</v>
       </c>
     </row>
-    <row r="14" spans="1:5" outlineLevel="3">
+    <row r="14" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1885,7 +1850,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:5" outlineLevel="3">
+    <row r="15" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1906,7 +1871,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:5" outlineLevel="3">
+    <row r="16" spans="1:5" outlineLevel="3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1927,7 +1892,7 @@
         <v>fizzbuzz</v>
       </c>
     </row>
-    <row r="17" spans="1:5" outlineLevel="1">
+    <row r="17" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1948,7 +1913,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:5" outlineLevel="1">
+    <row r="18" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1969,7 +1934,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:5" outlineLevel="1">
+    <row r="19" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1990,7 +1955,7 @@
         <v>fizz</v>
       </c>
     </row>
-    <row r="20" spans="1:5" outlineLevel="1">
+    <row r="20" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2011,7 +1976,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:5" outlineLevel="1">
+    <row r="21" spans="1:5" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2047,57 +2012,57 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet2" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A4:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="1" max="1" width="13.296875" customWidth="1"/>
+    <col min="2" max="2" width="15.796875" customWidth="1"/>
     <col min="3" max="3" width="5" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="4" max="4" width="10.796875" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="4.33203125" customWidth="1"/>
-    <col min="9" max="9" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.33203125" customWidth="1"/>
-    <col min="17" max="17" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="5.33203125" customWidth="1"/>
-    <col min="19" max="19" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="7.83203125" customWidth="1"/>
-    <col min="24" max="24" width="7.1640625" customWidth="1"/>
+    <col min="7" max="7" width="17.69921875" customWidth="1"/>
+    <col min="8" max="8" width="4.296875" customWidth="1"/>
+    <col min="9" max="9" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.796875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.296875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.296875" customWidth="1"/>
+    <col min="17" max="17" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.296875" customWidth="1"/>
+    <col min="19" max="19" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.796875" customWidth="1"/>
+    <col min="24" max="24" width="7.19921875" customWidth="1"/>
     <col min="25" max="25" width="9.5" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="6" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="10.83203125" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.796875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.19921875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="5.296875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="5.296875" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="5.296875" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="5.296875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="5.296875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2105,7 +2070,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2116,51 +2081,48 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="4"/>
-      <c r="B7" s="3">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7">
         <v>11</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7">
         <v>3</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>5</v>
       </c>
-      <c r="C8" s="3">
-        <v>1</v>
-      </c>
-      <c r="D8" s="3">
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>16</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9">
         <v>20</v>
       </c>
     </row>
@@ -2180,99 +2142,99 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr codeName="Sheet3" enableFormatConditionsCalculation="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="17" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="23" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="5" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="9" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="11" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="14"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="24"/>
-      <c r="B7" s="15">
+      <c r="B6" s="7"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="19"/>
+      <c r="B7" s="11">
         <v>0.9</v>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="12">
         <v>1.5</v>
       </c>
-      <c r="D7" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="24" t="s">
+      <c r="D7" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="11">
         <v>1.2</v>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="12">
         <v>0</v>
       </c>
-      <c r="D8" s="17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="18" t="s">
+      <c r="D8" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="19">
-        <v>1</v>
-      </c>
-      <c r="C9" s="20">
-        <v>1</v>
-      </c>
-      <c r="D9" s="21">
+      <c r="B9" s="15">
+        <v>1</v>
+      </c>
+      <c r="C9" s="16">
+        <v>1</v>
+      </c>
+      <c r="D9" s="17">
         <v>1</v>
       </c>
     </row>
